--- a/data-raw/metadata/battle_surveyed_reaches_metadata.xlsx
+++ b/data-raw/metadata/battle_surveyed_reaches_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Badhia\Documents\git\jpe-battle-adult-edi\data-raw\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25CB3E4-4714-4A77-A1FE-6660E1FECA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C47991-3D5D-44E6-9DA9-404D94D71493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6400" yWindow="680" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,9 +94,6 @@
     <t>reach</t>
   </si>
   <si>
-    <t>Survey reach where redd was located. Levels =c("R1", "R3", "R2", "R4", "R5", "R6", "R7", "R2A", "R2B", "R4A", "R4B", "R1A", "R1B", "R2b, 4a", "R4b", "R2a", "R2B/4", "R6B", "R2b" )</t>
-  </si>
-  <si>
     <t>Date when survey was conducted</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
   </si>
   <si>
     <t>10/30/2024</t>
+  </si>
+  <si>
+    <t>Survey reach where redd was located. Levels =c("R1", "R3", "R2", "R4", "R5", "R6", "R7", "R2A", "R2B", "R4A", "R4B", "R1A", "R1B", "R2b/4a", "R4b", "R2a", "R2B/4", "R6B", "R2b" )</t>
   </si>
 </sst>
 </file>
@@ -518,13 +518,13 @@
         <v>19</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>15</v>
@@ -538,10 +538,10 @@
       </c>
       <c r="K2" s="14"/>
       <c r="L2" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
@@ -562,13 +562,13 @@
         <v>21</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>14</v>
